--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_76_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_76_IN_Piura.xlsx
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>9.45</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>36.41</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="C12" s="31">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>45.91</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>8.23</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1917,11 +1917,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>19.6151</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>8.9956</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>45.86</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1967,11 +1967,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>10.6195</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>54.14</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2146,11 +2146,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>19.6187</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2269,6 +2269,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2554,6 +2555,7 @@
       <c r="F18" s="17" t="inlineStr"/>
       <c r="G18" s="17" t="inlineStr"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -2598,6 +2600,7 @@
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23" ht="180" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
@@ -3015,11 +3018,11 @@
       </c>
       <c r="B18" s="33">
         <f>SUM(B10:B17)</f>
-        <v/>
+        <v>523.87</v>
       </c>
       <c r="C18" s="23">
         <f>SUM(C10:C17)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -3029,19 +3032,19 @@
       <c r="E18" s="17" t="inlineStr"/>
       <c r="F18" s="17">
         <f>ROUND(AVERAGE(F10:F17),2)</f>
-        <v/>
+        <v>28.06</v>
       </c>
       <c r="G18" s="22">
         <f>ROUND(AVERAGE(G10:G17),4)</f>
-        <v/>
+        <v>0.5477</v>
       </c>
       <c r="H18" s="23">
         <f>ROUND(AVERAGE(H10:H17),2)</f>
-        <v/>
+        <v>72.48</v>
       </c>
       <c r="I18" s="23">
         <f>ROUND(AVERAGE(I10:I17),2)</f>
-        <v/>
+        <v>31.88</v>
       </c>
     </row>
     <row r="19"/>
